--- a/out/Attention-mamba2_repeat_1_000002.xlsx
+++ b/out/Attention-mamba2_repeat_1_000002.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-mamba2_repeat_1_000002.xlsx
+++ b/out/Attention-mamba2_repeat_1_000002.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83617,14 +83617,14 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84412,14 +84412,14 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93157,14 +93157,14 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94747,14 +94747,14 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-mamba2_repeat_1_000002.xlsx
+++ b/out/Attention-mamba2_repeat_1_000002.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.192729264497757</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999997</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.3515121638774872</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2999999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.246302530169487</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.1579521745443344</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.2341721802949905</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.1867095679044724</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.1324348747730255</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.3202944099903107</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.5248058438301086</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.3026683628559113</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.1590408384799957</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.08547315001487732</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.1709001660346985</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.1199108958244324</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.1016549170017242</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.1134347915649414</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.1370590478181839</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.1281677782535553</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.1034081354737282</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.1097326874732971</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.1303607523441315</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.1008842140436172</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.09030184149742126</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.4793422222137451</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.2969483733177185</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.2113465070724487</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.2173815816640854</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.1784853935241699</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.118044450879097</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.1006451696157455</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.1220993101596832</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.09233205020427704</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.09623951464891434</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.1092840284109116</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.1938524693250656</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.4117897152900696</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.3119461536407471</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.2152228504419327</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.5045732259750366</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.5774978995323181</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.5936818718910217</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.5605074763298035</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.5154200196266174</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.4155758917331696</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.4623252749443054</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.5098939538002014</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.5406914353370667</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.5017088055610657</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.579319179058075</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.4996145069599152</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.5025060176849365</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.5271232724189758</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.4696253538131714</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.3551701605319977</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.4037509262561798</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.2091956585645676</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.2782482206821442</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.4790143072605133</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.4741352498531342</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.4899234473705292</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.5003008246421814</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.4584973752498627</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.3410412967205048</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.5281801223754883</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.5549514293670654</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.5145672559738159</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.4981402456760406</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.5128408074378967</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.3949178159236908</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.3296809792518616</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.3042837679386139</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.3207177817821503</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.1760086864233017</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.3036758303642273</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.1010796800255775</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.1071010008454323</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.1996584981679916</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.1456887423992157</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.1055547073483467</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.1222763508558273</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.1294568926095963</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.2464337646961212</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.1270869821310043</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.1494039744138718</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.1328442245721817</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.04857104644179344</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.1746063679456711</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.295161098241806</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.3330739438533783</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.213978499174118</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.1684607267379761</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.3629377782344818</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.1476899981498718</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.08654990792274475</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.05042216926813126</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.3050918877124786</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.1356037110090256</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.1419240981340408</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.08632050454616547</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.2128383070230484</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.06821519136428833</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.109628938138485</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83617,14 +83617,14 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.1683728992938995</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84412,14 +84412,14 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.1102817133069038</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.1404448449611664</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.131857305765152</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.09657774120569229</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.07894240319728851</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.1039433851838112</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.0698811337351799</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.1633061766624451</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.1018202006816864</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.1302336156368256</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.09542711079120636</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93157,14 +93157,14 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.1286914348602295</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.2614621818065643</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94747,14 +94747,14 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.4646377861499786</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.3993798792362213</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.4054900109767914</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.3517642319202423</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.4055871963500977</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.3323042392730713</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.4053410589694977</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.2699132859706879</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.4462430775165558</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999996</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-mamba2_repeat_1_000002.xlsx
+++ b/out/Attention-mamba2_repeat_1_000002.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.192729264497757</v>
+        <v>-0.1927351504564285</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.5799999999999997</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.3515121638774872</v>
+        <v>-0.3515172004699707</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.2999999999999997</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.246302530169487</v>
+        <v>-0.2463076561689377</v>
       </c>
       <c r="JB4" t="n">
         <v>0.5799999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.1579521745443344</v>
+        <v>-0.1579568535089493</v>
       </c>
       <c r="JB5" t="n">
         <v>0.7199999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.2341721802949905</v>
+        <v>-0.2341770380735397</v>
       </c>
       <c r="JB6" t="n">
         <v>0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.1867095679044724</v>
+        <v>-0.1867145150899887</v>
       </c>
       <c r="JB7" t="n">
         <v>0.7199999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.1324348747730255</v>
+        <v>-0.1324394792318344</v>
       </c>
       <c r="JB8" t="n">
         <v>0.4399999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.3202944099903107</v>
+        <v>-0.3202991485595703</v>
       </c>
       <c r="JB9" t="n">
         <v>0.16</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.5248058438301086</v>
+        <v>-0.5248101353645325</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.4399999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.3026683628559113</v>
+        <v>-0.3026731014251709</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.4399999999999999</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.1590408384799957</v>
+        <v>-0.1590456813573837</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.16</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.08547315001487732</v>
+        <v>-0.08547747880220413</v>
       </c>
       <c r="JB13" t="n">
         <v>0.1199999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.1709001660346985</v>
+        <v>-0.1709049046039581</v>
       </c>
       <c r="JB14" t="n">
         <v>0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.1199108958244324</v>
+        <v>-0.1199154406785965</v>
       </c>
       <c r="JB15" t="n">
         <v>0.9999999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.1016549170017242</v>
+        <v>-0.1016595363616943</v>
       </c>
       <c r="JB16" t="n">
         <v>0.8599999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.1134347915649414</v>
+        <v>-0.1134393215179443</v>
       </c>
       <c r="JB17" t="n">
         <v>0.8599999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.1370590478181839</v>
+        <v>-0.1370636522769928</v>
       </c>
       <c r="JB18" t="n">
         <v>0.8599999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.1281677782535553</v>
+        <v>-0.1281723231077194</v>
       </c>
       <c r="JB19" t="n">
         <v>0.7199999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.1034081354737282</v>
+        <v>-0.1034126058220863</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.02000000000000007</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.1097326874732971</v>
+        <v>-0.1097371950745583</v>
       </c>
       <c r="JB21" t="n">
         <v>0.1199999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.1303607523441315</v>
+        <v>-0.1303652375936508</v>
       </c>
       <c r="JB22" t="n">
         <v>0.1199999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.1008842140436172</v>
+        <v>-0.100888691842556</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.16</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.09030184149742126</v>
+        <v>-0.0903058797121048</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.3</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.4793422222137451</v>
+        <v>-0.479346752166748</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.4399999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.2969483733177185</v>
+        <v>-0.2969528436660767</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.7199999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.2113465070724487</v>
+        <v>-0.2113510370254517</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.8599999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.2173815816640854</v>
+        <v>-0.2173861116170883</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.5799999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.1784853935241699</v>
+        <v>-0.1784899979829788</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.3</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.118044450879097</v>
+        <v>-0.1180489361286163</v>
       </c>
       <c r="JB30" t="n">
         <v>0.5799999999999998</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.1006451696157455</v>
+        <v>-0.1006496548652649</v>
       </c>
       <c r="JB31" t="n">
         <v>0.8599999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.1220993101596832</v>
+        <v>-0.1221038997173309</v>
       </c>
       <c r="JB32" t="n">
         <v>0.9999999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.09233205020427704</v>
+        <v>-0.09233646094799042</v>
       </c>
       <c r="JB33" t="n">
         <v>0.9999999999999998</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.09623951464891434</v>
+        <v>-0.09624400734901428</v>
       </c>
       <c r="JB34" t="n">
         <v>0.7199999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.1092840284109116</v>
+        <v>-0.1092884466052055</v>
       </c>
       <c r="JB35" t="n">
         <v>0.4399999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.1938524693250656</v>
+        <v>-0.1938567906618118</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.4399999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.4117897152900696</v>
+        <v>-0.4117940068244934</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.7199999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.3119461536407471</v>
+        <v>-0.3119508028030396</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.2152228504419327</v>
+        <v>-0.2152270823717117</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.5045732259750366</v>
+        <v>-0.5045773983001709</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.5774978995323181</v>
+        <v>-0.5775018930435181</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.5936818718910217</v>
+        <v>-0.5936858057975769</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.5605074763298035</v>
+        <v>-0.5605068802833557</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.5154200196266174</v>
+        <v>-0.5154184699058533</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.4155758917331696</v>
+        <v>-0.4155734777450562</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.4623252749443054</v>
+        <v>-0.4623234570026398</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.5098939538002014</v>
+        <v>-0.5098922848701477</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.5406914353370667</v>
+        <v>-0.5406911969184875</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.5017088055610657</v>
+        <v>-0.5017072558403015</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.579319179058075</v>
+        <v>-0.5793191194534302</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.4996145069599152</v>
+        <v>-0.4996132254600525</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.5025060176849365</v>
+        <v>-0.5025042295455933</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.5271232724189758</v>
+        <v>-0.5271216630935669</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.2599999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.4696253538131714</v>
+        <v>-0.4696239233016968</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.2599999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.3551701605319977</v>
+        <v>-0.3551703095436096</v>
       </c>
       <c r="JB55" t="n">
         <v>0.02000000000000007</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.4037509262561798</v>
+        <v>-0.4037494361400604</v>
       </c>
       <c r="JB56" t="n">
         <v>0.3</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.2782482206821442</v>
+        <v>-0.2782481014728546</v>
       </c>
       <c r="JB58" t="n">
         <v>0.1600000000000001</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.4790143072605133</v>
+        <v>-0.4790130853652954</v>
       </c>
       <c r="JB59" t="n">
         <v>0.16</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.4741352498531342</v>
+        <v>-0.4741340279579163</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.1199999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.4899234473705292</v>
+        <v>-0.4899232089519501</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.5003008246421814</v>
+        <v>-0.5002993941307068</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.7199999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.4584973752498627</v>
+        <v>-0.4584959745407104</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.7199999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.3410412967205048</v>
+        <v>-0.3410412669181824</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.7199999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.5281801223754883</v>
+        <v>-0.5281795859336853</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.7199999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.5549514293670654</v>
+        <v>-0.5549505352973938</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.7199999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.5145672559738159</v>
+        <v>-0.514565646648407</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.4981402456760406</v>
+        <v>-0.4981382191181183</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.7199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.5128408074378967</v>
+        <v>-0.5128394961357117</v>
       </c>
       <c r="JB69" t="n">
         <v>0.16</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.3949178159236908</v>
+        <v>-0.3949171304702759</v>
       </c>
       <c r="JB70" t="n">
         <v>0.4399999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.3296809792518616</v>
+        <v>-0.3296807408332825</v>
       </c>
       <c r="JB71" t="n">
         <v>0.7199999999999999</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.3042837679386139</v>
+        <v>-0.3042829036712646</v>
       </c>
       <c r="JB72" t="n">
         <v>0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.3207177817821503</v>
+        <v>-0.3207224309444427</v>
       </c>
       <c r="JB73" t="n">
         <v>0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.1760086864233017</v>
+        <v>-0.1760085076093674</v>
       </c>
       <c r="JB74" t="n">
         <v>0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.3036758303642273</v>
+        <v>-0.3036808669567108</v>
       </c>
       <c r="JB75" t="n">
         <v>0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.1010796800255775</v>
+        <v>-0.1010850593447685</v>
       </c>
       <c r="JB76" t="n">
         <v>0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.1071010008454323</v>
+        <v>-0.1071062311530113</v>
       </c>
       <c r="JB77" t="n">
         <v>0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.1996584981679916</v>
+        <v>-0.1996632516384125</v>
       </c>
       <c r="JB78" t="n">
         <v>0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.1456887423992157</v>
+        <v>-0.1456933319568634</v>
       </c>
       <c r="JB79" t="n">
         <v>0.8599999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.1055547073483467</v>
+        <v>-0.1055599600076675</v>
       </c>
       <c r="JB80" t="n">
         <v>0.1199999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.1222763508558273</v>
+        <v>-0.1222809329628944</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.02000000000000007</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.1294568926095963</v>
+        <v>-0.129461333155632</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.02000000000000007</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.2464337646961212</v>
+        <v>-0.2464385479688644</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.16</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.1270869821310043</v>
+        <v>-0.1270916014909744</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.16</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.1494039744138718</v>
+        <v>-0.149408683180809</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.02000000000000007</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.1328442245721817</v>
+        <v>-0.1328490823507309</v>
       </c>
       <c r="JB86" t="n">
         <v>0.1199999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.04857104644179344</v>
+        <v>-0.04857496172189713</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.02000000000000007</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.1746063679456711</v>
+        <v>-0.1746107488870621</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.16</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.295161098241806</v>
+        <v>-0.2951652705669403</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.16</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.3330739438533783</v>
+        <v>-0.3330723643302917</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.3</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.213978499174118</v>
+        <v>-0.2139827162027359</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.5799999999999998</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.1684607267379761</v>
+        <v>-0.1684650480747223</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.4399999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.3629377782344818</v>
+        <v>-0.3629425764083862</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.1600000000000001</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.1476899981498718</v>
+        <v>-0.1476944535970688</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.02000000000000007</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.08654990792274475</v>
+        <v>-0.08655419200658798</v>
       </c>
       <c r="JB95" t="n">
         <v>0.4399999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.05042216926813126</v>
+        <v>-0.0504257008433342</v>
       </c>
       <c r="JB96" t="n">
         <v>0.7199999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.3050918877124786</v>
+        <v>-0.3050965666770935</v>
       </c>
       <c r="JB97" t="n">
         <v>0.7199999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.1356037110090256</v>
+        <v>-0.135607972741127</v>
       </c>
       <c r="JB98" t="n">
         <v>0.7199999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.1419240981340408</v>
+        <v>-0.1419284790754318</v>
       </c>
       <c r="JB99" t="n">
         <v>0.4399999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.08632050454616547</v>
+        <v>-0.08632458001375198</v>
       </c>
       <c r="JB100" t="n">
         <v>0.7199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.2128383070230484</v>
+        <v>-0.2128428071737289</v>
       </c>
       <c r="JB101" t="n">
         <v>0.7199999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.06821519136428833</v>
+        <v>-0.06821919977664948</v>
       </c>
       <c r="JB102" t="n">
         <v>0.5799999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.109628938138485</v>
+        <v>-0.1096330806612968</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.16</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.1683728992938995</v>
+        <v>-0.1683771163225174</v>
       </c>
       <c r="JB104" t="n">
         <v>0.1199999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.1102817133069038</v>
+        <v>-0.1102858036756516</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.02000000000000007</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.1404448449611664</v>
+        <v>-0.1404490917921066</v>
       </c>
       <c r="JB106" t="n">
         <v>0.5799999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.131857305765152</v>
+        <v>-0.1318615227937698</v>
       </c>
       <c r="JB107" t="n">
         <v>0.7199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.09657774120569229</v>
+        <v>-0.09658182412385941</v>
       </c>
       <c r="JB108" t="n">
         <v>0.8599999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.07894240319728851</v>
+        <v>-0.07894639670848846</v>
       </c>
       <c r="JB109" t="n">
         <v>0.8599999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.1039433851838112</v>
+        <v>-0.1039475500583649</v>
       </c>
       <c r="JB110" t="n">
         <v>0.8599999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.0698811337351799</v>
+        <v>-0.06988503783941269</v>
       </c>
       <c r="JB111" t="n">
         <v>0.7199999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.1633061766624451</v>
+        <v>-0.1633104830980301</v>
       </c>
       <c r="JB112" t="n">
         <v>0.5799999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.1018202006816864</v>
+        <v>-0.1018241792917252</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.02000000000000007</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.1302336156368256</v>
+        <v>-0.130237802863121</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.16</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.09542711079120636</v>
+        <v>-0.09543120861053467</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.3</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.1286914348602295</v>
+        <v>-0.128695160150528</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.4399999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.2614621818065643</v>
+        <v>-0.2614611089229584</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.5799999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.4646377861499786</v>
+        <v>-0.464618444442749</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.8599999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.3993798792362213</v>
+        <v>-0.3993777930736542</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.9999999999999998</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.4054900109767914</v>
+        <v>-0.4054897427558899</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.9999999999999998</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.3517642319202423</v>
+        <v>-0.3517630100250244</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.9999999999999998</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.4055871963500977</v>
+        <v>-0.4055913686752319</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.9999999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.3323042392730713</v>
+        <v>-0.3323082327842712</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.9999999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.4053410589694977</v>
+        <v>-0.40534508228302</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.9999999999999998</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.2699132859706879</v>
+        <v>-0.2699172794818878</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.9999999999999996</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.4462430775165558</v>
+        <v>-0.4462432265281677</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.9999999999999996</v>
